--- a/artfynd/A 14059-2023 artfynd.xlsx
+++ b/artfynd/A 14059-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14059-2023 artfynd.xlsx
+++ b/artfynd/A 14059-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>480007</v>
+        <v>129033</v>
       </c>
       <c r="B2" t="n">
-        <v>89544</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1503</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421664.0958494947</v>
+        <v>421770</v>
       </c>
       <c r="R2" t="n">
-        <v>6899230.08897494</v>
+        <v>6899235</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2008-05-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-05-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olli Manninen, Elina Hinkkanen, Eva Ydrén, * Naturskyddare, Päivi Mattila</t>
+          <t>Olli Manninen, Eva Ydrén, Elina Hinkkanen, * Naturskyddare, Päivi Mattila</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -801,37 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>678661</v>
+        <v>480000</v>
       </c>
       <c r="B3" t="n">
-        <v>90840</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421781.2865145224</v>
+        <v>421709</v>
       </c>
       <c r="R3" t="n">
-        <v>6899265.62917975</v>
+        <v>6899141</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,19 +854,9 @@
           <t>2008-05-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-05-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olli Manninen, * Naturskyddare, Eva Ydrén, Elina Hinkkanen, Päivi Mattila</t>
+          <t>Olli Manninen, Päivi Mattila, Elina Hinkkanen, Eva Ydrén, * Naturskyddare</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -927,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>480000</v>
+        <v>480007</v>
       </c>
       <c r="B4" t="n">
-        <v>89544</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421709.2209562197</v>
+        <v>421664</v>
       </c>
       <c r="R4" t="n">
-        <v>6899140.842093668</v>
+        <v>6899230</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1000,19 +965,9 @@
           <t>2008-05-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2008-05-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olli Manninen, Päivi Mattila, Elina Hinkkanen, Eva Ydrén, * Naturskyddare</t>
+          <t>Olli Manninen, Elina Hinkkanen, Eva Ydrén, * Naturskyddare, Päivi Mattila</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1053,37 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129033</v>
+        <v>678649</v>
       </c>
       <c r="B5" t="n">
-        <v>89632</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421769.8178116498</v>
+        <v>421709</v>
       </c>
       <c r="R5" t="n">
-        <v>6899234.630564637</v>
+        <v>6899141</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1126,19 +1076,9 @@
           <t>2008-05-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2008-05-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,7 +1108,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olli Manninen, Eva Ydrén, Elina Hinkkanen, * Naturskyddare, Päivi Mattila</t>
+          <t>Olli Manninen, * Naturskyddare, Eva Ydrén, Elina Hinkkanen, Päivi Mattila</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1179,15 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>678649</v>
+        <v>678661</v>
       </c>
       <c r="B6" t="n">
-        <v>90840</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>421709.2209562197</v>
+        <v>421781</v>
       </c>
       <c r="R6" t="n">
-        <v>6899140.842093668</v>
+        <v>6899266</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1252,19 +1187,9 @@
           <t>2008-05-22</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2008-05-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,15 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>820838</v>
+        <v>820835</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421721.2902074254</v>
+        <v>421737</v>
       </c>
       <c r="R7" t="n">
-        <v>6899117.228481147</v>
+        <v>6899011</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1378,19 +1298,9 @@
           <t>2008-05-22</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2008-05-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,10 +1325,116 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
+          <t>Olli Manninen, Eva Ydrén, Elina Hinkkanen, * Naturskyddare, Päivi Mattila</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddare</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>820838</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80433</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hovdhållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>421721</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6899117</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Linsell</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2008-05-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2008-05-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Olli Manninen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
           <t>Olli Manninen, Elina Hinkkanen, Päivi Mattila, Eva Ydrén, * Naturskyddare</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Naturskyddare</t>
         </is>

--- a/artfynd/A 14059-2023 artfynd.xlsx
+++ b/artfynd/A 14059-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129033</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/480000</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/480007</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/678649</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/678661</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1333,6 +1363,11 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/820835</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,8 +1474,22 @@
           <t>Naturskyddare</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/820838</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>